--- a/src/conf/coding_schema/coding_schema.xlsx
+++ b/src/conf/coding_schema/coding_schema.xlsx
@@ -4,11 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11040" firstSheet="7" activeTab="12"/>
+    <workbookView windowWidth="28800" windowHeight="11040"/>
   </bookViews>
   <sheets>
-    <sheet name="Digital Technology" sheetId="1" r:id="rId1"/>
-    <sheet name="Tacit Knowledge" sheetId="13" r:id="rId2"/>
+    <sheet name="Tacit Knowledge" sheetId="13" r:id="rId1"/>
+    <sheet name="Digital Technology" sheetId="1" r:id="rId2"/>
     <sheet name="Traditional Human-central Pract" sheetId="7" r:id="rId3"/>
     <sheet name="Environmental Dependency" sheetId="8" r:id="rId4"/>
     <sheet name="Organizational Dependency" sheetId="10" r:id="rId5"/>
@@ -17,12 +17,12 @@
     <sheet name="Technology-enable Practice" sheetId="12" r:id="rId8"/>
     <sheet name="RAG Performance" sheetId="2" r:id="rId9"/>
     <sheet name="Entity" sheetId="3" r:id="rId10"/>
-    <sheet name="edge" sheetId="4" r:id="rId11"/>
+    <sheet name="Edge" sheetId="4" r:id="rId11"/>
     <sheet name="downstream_task" sheetId="5" r:id="rId12"/>
     <sheet name="RQ Coding" sheetId="14" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Technology-enable Practice'!$A$1:$E$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Technology-enable Practice'!$A$1:$E$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'RQ Coding'!$B:$B</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="399">
   <si>
     <t>ID</t>
   </si>
@@ -57,6 +57,51 @@
     <t>Example</t>
   </si>
   <si>
+    <t>TK01</t>
+  </si>
+  <si>
+    <t>Relational Tacit Knowledge</t>
+  </si>
+  <si>
+    <t>knowledge that could be made explicit in principle but remains unstated because of social contingencies—secrecy, lack of communication effort, asymmetric trust, unequal access, or practical cost of documentation.</t>
+  </si>
+  <si>
+    <t>Trade secrets held by craft workers or industrial technicians, never written into standard operating manuals;
+Workplace unspoken norms: knowing when not to raise sensitive requests to supervisors;
+Warehouse veterans’ mental map of shelf layouts—never catalogued formally, only passed verbally on demand;
+Confidential negotiation tactics kept hidden from competitors.</t>
+  </si>
+  <si>
+    <t>TK02</t>
+  </si>
+  <si>
+    <t>Somatic Tacit Knowledge</t>
+  </si>
+  <si>
+    <t>Knowledge that is embedded in human bodily and neurophysiological capacities</t>
+  </si>
+  <si>
+    <t>A cyclist's skill in keeping balance while riding a bicycle;
+Surgeon’s fine motor tension control during suturing;
+Musicians’ subtle hand pressure for tone;
+Pilots’ bodily sensory anticipation of aircraft stall before instrument alerts.</t>
+  </si>
+  <si>
+    <t>TK03</t>
+  </si>
+  <si>
+    <t>Collective Tacit Knowledge</t>
+  </si>
+  <si>
+    <t>Knowledge that belongs not to individual bodies or isolated minds but to social collectivities, embedded in shared cultural, linguistic and communal practice, cannot be fully unpacked into context-free written rules independent of social immersion.</t>
+  </si>
+  <si>
+    <t>Traffic social conventions like knowing how to make eye contact with drivers at busy junctions in just the way necessary to assure a safe passage and not to invite an unwanted response;
+Scientific community unspoken standards for judging valid experimental evidence;
+Sports team synchronized nonverbal coordination (pit crew, football line coordination);
+Cross-cultural ritual and etiquette judgments only learned through long social participation.</t>
+  </si>
+  <si>
     <t>TE01</t>
   </si>
   <si>
@@ -162,141 +207,6 @@
     <t>Digital Technology, but excludes TE01-TE08</t>
   </si>
   <si>
-    <t>TK01</t>
-  </si>
-  <si>
-    <t>Somatic experiential know-how</t>
-  </si>
-  <si>
-    <t>Deep-seated patterns from years of exposure.</t>
-  </si>
-  <si>
-    <t>A senior pilot "feeling" a stall before the instruments react.</t>
-  </si>
-  <si>
-    <t>TK02</t>
-  </si>
-  <si>
-    <t>Somatic procedural know-how</t>
-  </si>
-  <si>
-    <t>The "knack" for fluid execution.</t>
-  </si>
-  <si>
-    <t>A surgeon knowing exactly how much tension to put on a specific suture.</t>
-  </si>
-  <si>
-    <t>TK03</t>
-  </si>
-  <si>
-    <t>Somatic craft knowledge</t>
-  </si>
-  <si>
-    <t>Sensory expertise (haptics/sight).</t>
-  </si>
-  <si>
-    <t>A master brewer knowing a fermentation is ready by the "nose" of the vat.</t>
-  </si>
-  <si>
-    <t>TK04</t>
-  </si>
-  <si>
-    <t>Somatic operational know-how</t>
-  </si>
-  <si>
-    <t>Unique "tribal knowledge" of specific systems.</t>
-  </si>
-  <si>
-    <t>A technician knowing that "Turbine 4" needs a specific wiggle to start in the cold.</t>
-  </si>
-  <si>
-    <t>TK05</t>
-  </si>
-  <si>
-    <t>Somatic others</t>
-  </si>
-  <si>
-    <t>Tacit knowledge which stores in some individual body, but excludes TK01-TK04</t>
-  </si>
-  <si>
-    <t>TK06</t>
-  </si>
-  <si>
-    <t>Cognitive expert judgment</t>
-  </si>
-  <si>
-    <t>Seeing the "whole" to make high-stakes calls.</t>
-  </si>
-  <si>
-    <t>A CEO sensing a market shift despite conflicting data reports.</t>
-  </si>
-  <si>
-    <t>TK07</t>
-  </si>
-  <si>
-    <t>Cognitive decision rules</t>
-  </si>
-  <si>
-    <t>Subconscious mental shortcuts (heuristics).</t>
-  </si>
-  <si>
-    <t>A buyer's rule: "If a supplier avoids eye contact during price talk, keep digging."</t>
-  </si>
-  <si>
-    <t>TK08</t>
-  </si>
-  <si>
-    <t>Cognitive clinical know-how</t>
-  </si>
-  <si>
-    <t>Diagnostic intuition for root causes.</t>
-  </si>
-  <si>
-    <t>An IT Architect spotting a network bottleneck from a single, unrelated log line.</t>
-  </si>
-  <si>
-    <t>TK09</t>
-  </si>
-  <si>
-    <t>Cognitive situational problem-solving</t>
-  </si>
-  <si>
-    <t>"Practical wisdom" to innovate in a crisis.</t>
-  </si>
-  <si>
-    <t>A logistics manager rerouting a fleet mid-storm when the GPS network goes down.</t>
-  </si>
-  <si>
-    <t>TK10</t>
-  </si>
-  <si>
-    <t>Cognitive others</t>
-  </si>
-  <si>
-    <t>Tacit knowledge which stores in some individual minds, but excludes TK06-TK09</t>
-  </si>
-  <si>
-    <t>TK11</t>
-  </si>
-  <si>
-    <t>Collective teamwork know-how</t>
-  </si>
-  <si>
-    <t>The "unspoken rhythm" of a social group.</t>
-  </si>
-  <si>
-    <t>A pit crew performing a tire change in 2 seconds without a single word spoken.</t>
-  </si>
-  <si>
-    <t>TK12</t>
-  </si>
-  <si>
-    <t>Collective others</t>
-  </si>
-  <si>
-    <t>Tacit knowledge which stores in some teams or groups, but excludes TK11</t>
-  </si>
-  <si>
     <t>THR01</t>
   </si>
   <si>
@@ -804,48 +714,7 @@
     <t>Accurately select options or generate verifiable answers based on facts within document corpora.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>88.98% factual accuracy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>MIRAGE benchmark</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, outperforming standalone LLMs by 14 percentage points (Punuru et al., 2025).</t>
-    </r>
+    <t>88.98% factual accuracy on the MIRAGE benchmark, outperforming standalone LLMs by 14 percentage points (Punuru et al., 2025).</t>
   </si>
   <si>
     <t>Text Structuring and Classification</t>
@@ -854,48 +723,7 @@
     <t>Categorize topics, viewpoints, emotions, or research types based on indexed text attributes.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>89.1% Context Precision</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> evaluated via the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RAGAS framework</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, verifying the system's ability to reliably isolate target categorical variables (Baur et al., 2024).</t>
-    </r>
+    <t>89.1% Context Precision evaluated via the RAGAS framework, verifying the system's ability to reliably isolate target categorical variables (Baur et al., 2024).</t>
   </si>
   <si>
     <t>Information Extraction</t>
@@ -904,48 +732,7 @@
     <t>Extract structured insights (entities, conclusions, indicators, causal relationships) from complex documents.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>93.0% Document-Level Recall</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>MedCPT benchmark</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, demonstrating highly reliable discovery of granular data points within dense academic texts (Zhang et al., 2026).</t>
-    </r>
+    <t>93.0% Document-Level Recall on the MedCPT benchmark, demonstrating highly reliable discovery of granular data points within dense academic texts (Zhang et al., 2026).</t>
   </si>
   <si>
     <t>Document Summarization</t>
@@ -954,54 +741,16 @@
     <t>Integrate multi-document viewpoints and conclusions while maintaining strict consistency with source materials.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>85.3% Generation Faithfulness</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> measured via the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RAGAS framework</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, confirming that compiled summaries remain strictly anchored to original text baselines (Baur et al., 2024).</t>
-    </r>
-  </si>
-  <si>
-    <t>Entity category</t>
-  </si>
-  <si>
-    <t>Explicit knowledge</t>
+    <t>85.3% Generation Faithfulness measured via the RAGAS framework, confirming that compiled summaries remain strictly anchored to original text baselines (Baur et al., 2024).</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Node Name</t>
+  </si>
+  <si>
+    <t>Explicit Knowledge</t>
   </si>
   <si>
     <t>Codified, documented, or materialised forms of knowledge that can be stored, accessed, or reused. These artifacts may serve as carriers or outputs of knowledge retention.</t>
@@ -1010,303 +759,295 @@
     <t>Manuals; reports; databases; standard operating procedures; design documents; videos; digital records; training materials</t>
   </si>
   <si>
+    <t>Tacit Knowledge</t>
+  </si>
+  <si>
+    <t>Experience-based, practice-based, embodied, contextual, or difficult-to-codify knowledge involved in the case. These elements are often held by individuals or groups and may be only partially represented through technology.</t>
+  </si>
+  <si>
+    <t>Expert judgement; diagnostic know-how; procedural experience; craft skills; situational awareness; troubleshooting experience; cultural practice knowledge</t>
+  </si>
+  <si>
+    <t>Knowledge Holder</t>
+  </si>
+  <si>
+    <t>Individuals, groups, communities, or organizational actors who possess or perform the relevant tacit knowledge.</t>
+  </si>
+  <si>
+    <t>Senior engineers; experts; technicians; operators; experienced employees; local practitioners; community members</t>
+  </si>
+  <si>
+    <t>Traditional Human-Centred Practice</t>
+  </si>
+  <si>
+    <t>Conventional knowledge retention or transfer practices that rely primarily on human interaction, social learning, participation, or manual documentation.</t>
+  </si>
+  <si>
+    <t>Mentoring; apprenticeship; storytelling; observation; meetings; after-action reviews; manual handover; community practice; face-to-face training</t>
+  </si>
+  <si>
+    <t>Technology-Enabled Practice</t>
+  </si>
+  <si>
+    <t>Knowledge retention practices supported, extended, or reshaped by emerging technologies. These practices involve the use of digital tools to capture or retain knowledge.</t>
+  </si>
+  <si>
+    <t>knowledge graph construction; digital twin simulation; VR training; AR guidance; IoT-based monitoring; expert system reasoning</t>
+  </si>
+  <si>
+    <t>Digital Technology</t>
+  </si>
+  <si>
+    <t>Specific emerging digital technologies adopted by Technology-enable Practice.</t>
+  </si>
+  <si>
+    <t>Virtual Reality; Artificial Intelligence; IoT; etc</t>
+  </si>
+  <si>
+    <t>Organization Dependency</t>
+  </si>
+  <si>
+    <t>Organizational, social, or cultural conditions that influence whether technology-enabled knowledge retention can work effectively.</t>
+  </si>
+  <si>
+    <t>Trust; psychological safety; leadership support; willingness to share; motivation; learning culture; expert participation; user acceptance</t>
+  </si>
+  <si>
+    <t>Environment Dependency</t>
+  </si>
+  <si>
+    <t>Specific external factor outside the organization's direct control required for the practice .</t>
+  </si>
+  <si>
+    <t>Industry regulation, Physical location constraint, Internet infrastructure</t>
+  </si>
+  <si>
+    <t>Limitation</t>
+  </si>
+  <si>
+    <t>Technical, organizational, data-related, or knowledge-related constraints that restrict the effectiveness of technology-enabled tacit knowledge retention.</t>
+  </si>
+  <si>
+    <t>Incomplete data; loss of contextual meaning; difficulty codifying embodied knowledge; high implementation cost; lack of technical infrastructure; weak user capability</t>
+  </si>
+  <si>
+    <t>Relation Type</t>
+  </si>
+  <si>
+    <t>Src Node Name</t>
+  </si>
+  <si>
+    <t>Dst Node Name</t>
+  </si>
+  <si>
+    <t>be_documented_partially_by</t>
+  </si>
+  <si>
+    <t>Use this when knowledge holder codify human experience, routines, or behaviors into structured text, files, or manuals.</t>
+  </si>
+  <si>
+    <t>Diagnostic know-how is documented partially by senior technician's personal logbook</t>
+  </si>
+  <si>
+    <t>translate_into</t>
+  </si>
+  <si>
+    <t>Use this when written rules, metrics, or guidelines are successfully put into practice by a person and turned into safe personal routines or hands-on skills.</t>
+  </si>
+  <si>
+    <t>Excavation safety knowledge translate into Real-time hazard identification performance. c001</t>
+  </si>
+  <si>
+    <t>be_held_by</t>
+  </si>
+  <si>
+    <t>Tacit Knowledge OR Explicit Knowledge</t>
+  </si>
+  <si>
+    <t>Use this to show the baseline location of an asset, identifying which specific person, expert, or team currently possesses that know-how or documentation.</t>
+  </si>
+  <si>
+    <t>Excavation safety knowledge is held by Construction professionals. c001</t>
+  </si>
+  <si>
+    <t>be_absorbed_by</t>
+  </si>
+  <si>
+    <t>Use this to mark a clear learning milestone, showing that a specific person or role has successfully gained new knowledge as a result of training.</t>
+  </si>
+  <si>
+    <t>Self-efficacy belief is absorbed by University students. c001</t>
+  </si>
+  <si>
+    <t>be_captured_by</t>
+  </si>
+  <si>
+    <t>Use this when human routines, actions, or real-time spatial behaviors are actively tracked or monitored inside a digital application or simulation.</t>
+  </si>
+  <si>
+    <t>Real-time hazard identification performance is captured by Immersive VR training system. c001</t>
+  </si>
+  <si>
+    <t>be_transferred_by</t>
+  </si>
+  <si>
+    <t>Traditional Human-Centred Practice OR Technology-Enabled Practice</t>
+  </si>
+  <si>
+    <t>Use this to connect a specific knowledge asset to the exact training vehicle, manual review, or simulation system used to distribute it.</t>
+  </si>
+  <si>
+    <t>Hazard identification skill is transferred by Immersive VR training system. c001</t>
+  </si>
+  <si>
+    <t>participate_in</t>
+  </si>
+  <si>
+    <t>Use this to map human actors to an operational workflow, showing who actively takes part in a chosen training approach or experiment.</t>
+  </si>
+  <si>
+    <t>University students participant in Immersive VR training system. c001</t>
+  </si>
+  <si>
+    <t>depend_on</t>
+  </si>
+  <si>
+    <t>Organization Dependency OR Environment Dependency</t>
+  </si>
+  <si>
+    <t>Use this to flag necessary baseline resources, company cultures, or external regulatory requirements needed for a practice to run successfully.</t>
+  </si>
+  <si>
+    <t>Immersive VR training system depend on Physical space (3m x 3m square). c001</t>
+  </si>
+  <si>
+    <t>evaluate</t>
+  </si>
+  <si>
+    <t>Technology-Enabled Practice OR Traditional Human-central Practice</t>
+  </si>
+  <si>
+    <t>Use this when a practice includes testing parameters, quizzes, or built-in performance scores designed to actively check a participant's skill or compliance level.</t>
+  </si>
+  <si>
+    <t>Immersive VR training system evaluate Real-time hazard identification performance. c001</t>
+  </si>
+  <si>
+    <t>adopt</t>
+  </si>
+  <si>
+    <t>Digital Technology OR Explicit Knowledge</t>
+  </si>
+  <si>
+    <t>Use this to outline system architecture, connecting a digital practice to its underlying physical hardware tools, software engines, or structural data files.</t>
+  </si>
+  <si>
+    <t>Immersive VR training system adopt Head Mounted Displays (Oculus Quest). c001</t>
+  </si>
+  <si>
+    <t>be_constrained_by</t>
+  </si>
+  <si>
+    <t>Use this to tie a practice directly to its known shortcomings, system bottlenecks, or real-world flaws, like steep human forgetting or passivity.</t>
+  </si>
+  <si>
+    <t>Health and safety manual self-study is constrained by Knowledge decay over time. c001</t>
+  </si>
+  <si>
+    <t>resolve</t>
+  </si>
+  <si>
+    <t>Use this only when verified data proves that a digital or automated approach completely removes or neutralizes an existing process bottleneck.</t>
+  </si>
+  <si>
+    <t>VR Exhibition Hall / Metaverse Scenario (NetEase Yaotai) resolve Fragmented scenarios (lack of wartime life recreation). c002</t>
+  </si>
+  <si>
+    <t>mitigate</t>
+  </si>
+  <si>
+    <t>Use this when an approach successfully lowers, softens, or controls a structural flaw or behavioral risk without completely eliminating it.</t>
+  </si>
+  <si>
+    <t>Immersive VR training system mitigate Knowledge-to-practice gap. c001</t>
+  </si>
+  <si>
+    <t>complement</t>
+  </si>
+  <si>
+    <t>Use this to show that a newly introduced digital framework enhances or patches a legacy human routine without making it obsolete.</t>
+  </si>
+  <si>
+    <t>3D Laser Scanning (FARO Focus S350 / Leica RTC360) complement Paper-based Surveying c002</t>
+  </si>
+  <si>
+    <t>cannot_fully_replace</t>
+  </si>
+  <si>
+    <t>Use this when case evidence proves that an automated tool still relies on human baselines, or that a physical practice remains legally mandatory.</t>
+  </si>
+  <si>
+    <t>Generative bid composition module cannot fully replace Human-in-the-loop review. c004</t>
+  </si>
+  <si>
+    <t>be_difficult_to_capture_due_to</t>
+  </si>
+  <si>
+    <t>Use this to map specific knowledge management roadblocks, explaining exactly what cognitive or process barriers prevent hands-on skills from being easily stored.</t>
+  </si>
+  <si>
+    <t>Real-time hazard identification performance is difficult to capture due to Knowledge-to-practice gap. c001</t>
+  </si>
+  <si>
+    <t>Object</t>
+  </si>
+  <si>
+    <t>Question</t>
+  </si>
+  <si>
+    <t>DS01Q01</t>
+  </si>
+  <si>
     <t>Tacit knowledge</t>
   </si>
   <si>
-    <t>Experience-based, practice-based, embodied, contextual, or difficult-to-codify knowledge involved in the case. These elements are often held by individuals or groups and may be only partially represented through technology.</t>
-  </si>
-  <si>
-    <t>Expert judgement; diagnostic know-how; procedural experience; craft skills; situational awareness; troubleshooting experience; cultural practice knowledge</t>
-  </si>
-  <si>
-    <t>Knowledge Holder</t>
-  </si>
-  <si>
-    <t>Individuals, groups, communities, or organizational actors who possess or perform the relevant tacit knowledge.</t>
-  </si>
-  <si>
-    <t>Senior engineers; experts; technicians; operators; experienced employees; local practitioners; community members</t>
+    <t>Which tacit knowledge is described?</t>
+  </si>
+  <si>
+    <t>DS01Q02</t>
+  </si>
+  <si>
+    <t>Which knowledge holders are described?</t>
+  </si>
+  <si>
+    <t>DS01Q03</t>
   </si>
   <si>
     <t>Traditional Human-centred Practices</t>
   </si>
   <si>
-    <t>Conventional knowledge retention or transfer practices that rely primarily on human interaction, social learning, participation, or manual documentation.</t>
-  </si>
-  <si>
-    <t>Mentoring; apprenticeship; storytelling; observation; meetings; after-action reviews; manual handover; community practice; face-to-face training</t>
+    <t>Which traditional human-centred practices are described?</t>
+  </si>
+  <si>
+    <t>DS01Q04</t>
   </si>
   <si>
     <t>Technology-enabled Practice</t>
   </si>
   <si>
-    <t>Knowledge retention practices supported, extended, or reshaped by emerging technologies. These practices involve the use of digital tools to capture or retain knowledge.</t>
-  </si>
-  <si>
-    <t>knowledge graph construction; digital twin simulation; VR training; AR guidance; IoT-based monitoring; expert system reasoning</t>
-  </si>
-  <si>
-    <t>Digital Technology</t>
-  </si>
-  <si>
-    <t>Specific emerging digital technologies adopted by Technology-enable Practice.</t>
-  </si>
-  <si>
-    <t>Virtual Reality; Artificial Intelligence; IoT; etc</t>
+    <t>Which technology‑enabled practices have been described?</t>
+  </si>
+  <si>
+    <t>DS01Q05</t>
+  </si>
+  <si>
+    <t>which emerging technologies have been described?</t>
+  </si>
+  <si>
+    <t>DS01Q06</t>
   </si>
   <si>
     <t>Organizational Dependency</t>
-  </si>
-  <si>
-    <t>Organizational, social, or cultural conditions that influence whether technology-enabled knowledge retention can work effectively.</t>
-  </si>
-  <si>
-    <t>Trust; psychological safety; leadership support; willingness to share; motivation; learning culture; expert participation; user acceptance</t>
-  </si>
-  <si>
-    <t>Environment Dependency</t>
-  </si>
-  <si>
-    <t>Specific external factor outside the organization's direct control required for the practice .</t>
-  </si>
-  <si>
-    <t>Industry regulation, Physical location constraint, Internet infrastructure</t>
-  </si>
-  <si>
-    <t>Limitation</t>
-  </si>
-  <si>
-    <t>Technical, organizational, data-related, or knowledge-related constraints that restrict the effectiveness of technology-enabled tacit knowledge retention.</t>
-  </si>
-  <si>
-    <t>Incomplete data; loss of contextual meaning; difficulty codifying embodied knowledge; high implementation cost; lack of technical infrastructure; weak user capability</t>
-  </si>
-  <si>
-    <t>Relation Type</t>
-  </si>
-  <si>
-    <t>Meaning</t>
-  </si>
-  <si>
-    <t>be_documented_partially_by</t>
-  </si>
-  <si>
-    <t>Use this when knowledge holder codify human experience, routines, or behaviors into structured text, files, or manuals.</t>
-  </si>
-  <si>
-    <t>Diagnostic know-how is documented partially by senior technician's personal logbook</t>
-  </si>
-  <si>
-    <t>be_derived_from</t>
-  </si>
-  <si>
-    <t>Use this to trace the origin or lineage of structured documents, showing that one file or rule was sourced directly from another standard text.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Seven critical hazards list is derived from OSHA Trenching and Excavation Safety guidelines </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[c001]</t>
-    </r>
-  </si>
-  <si>
-    <t>translate_into</t>
-  </si>
-  <si>
-    <t>Use this when written rules, metrics, or guidelines are successfully put into practice by a person and turned into safe personal routines or hands-on skills.</t>
-  </si>
-  <si>
-    <t>Excavation safety knowledge translate into Real-time hazard identification performance. [c001]</t>
-  </si>
-  <si>
-    <t>be_held_by</t>
-  </si>
-  <si>
-    <t>Use this to show the baseline location of an asset, identifying which specific person, expert, or team currently possesses that know-how or documentation.</t>
-  </si>
-  <si>
-    <t>Excavation safety knowledge is held by Construction professionals. [c001]</t>
-  </si>
-  <si>
-    <t>be_absorbed_by</t>
-  </si>
-  <si>
-    <t>Use this to mark a clear learning milestone, showing that a specific person or role has successfully gained new knowledge as a result of training.</t>
-  </si>
-  <si>
-    <t>Self-efficacy belief is absorbed by University students. [c001]</t>
-  </si>
-  <si>
-    <t>be_captured_by</t>
-  </si>
-  <si>
-    <t>Use this when human routines, actions, or real-time spatial behaviors are actively tracked or monitored inside a digital application or simulation.</t>
-  </si>
-  <si>
-    <t>Real-time hazard identification performance is captured by Immersive VR training system. [c001]</t>
-  </si>
-  <si>
-    <t>be_transferred_by</t>
-  </si>
-  <si>
-    <t>Use this to connect a specific knowledge asset to the exact training vehicle, manual review, or simulation system used to distribute it.</t>
-  </si>
-  <si>
-    <t>Hazard identification skill is transferred by Immersive VR training system. [c001]</t>
-  </si>
-  <si>
-    <t>participate_in</t>
-  </si>
-  <si>
-    <t>Use this to map human actors to an operational workflow, showing who actively takes part in a chosen training approach or experiment.</t>
-  </si>
-  <si>
-    <t>University students participant in Immersive VR training system. [c001]</t>
-  </si>
-  <si>
-    <t>depend_on</t>
-  </si>
-  <si>
-    <t>Use this to flag necessary baseline resources, company cultures, or external regulatory requirements needed for a practice to run successfully.</t>
-  </si>
-  <si>
-    <t>Immersive VR training system depend on Physical space (3m x 3m square). [c001]</t>
-  </si>
-  <si>
-    <t>evaluate</t>
-  </si>
-  <si>
-    <t>Use this when a practice includes testing parameters, quizzes, or built-in performance scores designed to actively check a participant's skill or compliance level.</t>
-  </si>
-  <si>
-    <t>Immersive VR training system evaluate Real-time hazard identification performance. [c001]</t>
-  </si>
-  <si>
-    <t>adopt</t>
-  </si>
-  <si>
-    <t>Use this to outline system architecture, connecting a digital practice to its underlying physical hardware tools, software engines, or structural data files.</t>
-  </si>
-  <si>
-    <t>Immersive VR training system adopt Head Mounted Displays (Oculus Quest). [c001]</t>
-  </si>
-  <si>
-    <t>be_constrained_by</t>
-  </si>
-  <si>
-    <t>Use this to tie a practice directly to its known shortcomings, system bottlenecks, or real-world flaws, like steep human forgetting or passivity.</t>
-  </si>
-  <si>
-    <t>Health and safety manual self-study is constrained by Knowledge decay over time. [c001]</t>
-  </si>
-  <si>
-    <t>resolve</t>
-  </si>
-  <si>
-    <t>Use this only when verified data proves that a digital or automated approach completely removes or neutralizes an existing process bottleneck.</t>
-  </si>
-  <si>
-    <t>VR Exhibition Hall / Metaverse Scenario (NetEase Yaotai) resolve Fragmented scenarios (lack of wartime life recreation). [c002]</t>
-  </si>
-  <si>
-    <t>mitigate</t>
-  </si>
-  <si>
-    <t>Use this when an approach successfully lowers, softens, or controls a structural flaw or behavioral risk without completely eliminating it.</t>
-  </si>
-  <si>
-    <t>Immersive VR training system mitigate Knowledge-to-practice gap. [c001]</t>
-  </si>
-  <si>
-    <t>complement</t>
-  </si>
-  <si>
-    <t>Use this to show that a newly introduced digital framework enhances or patches a legacy human routine without making it obsolete.</t>
-  </si>
-  <si>
-    <t>3D Laser Scanning (FARO Focus S350 / Leica RTC360) complement Paper-based Surveying [c002]</t>
-  </si>
-  <si>
-    <t>cannot_fully_replace</t>
-  </si>
-  <si>
-    <t>Use this when case evidence proves that an automated tool still relies on human baselines, or that a physical practice remains legally mandatory.</t>
-  </si>
-  <si>
-    <t>Generative bid composition module cannot fully replace Human-in-the-loop review. [c004]</t>
-  </si>
-  <si>
-    <t>be_difficult_to_capture_due_to</t>
-  </si>
-  <si>
-    <t>Use this to map specific knowledge management roadblocks, explaining exactly what cognitive or process barriers prevent hands-on skills from being easily stored.</t>
-  </si>
-  <si>
-    <t>Real-time hazard identification performance is difficult to capture due to Knowledge-to-practice gap. [c001]</t>
-  </si>
-  <si>
-    <t>Object</t>
-  </si>
-  <si>
-    <t>Question</t>
-  </si>
-  <si>
-    <t>DS01Q01</t>
-  </si>
-  <si>
-    <t>Which tacit knowledge is described?</t>
-  </si>
-  <si>
-    <t>DS01Q02</t>
-  </si>
-  <si>
-    <t>Which knowledge holders are described?</t>
-  </si>
-  <si>
-    <t>DS01Q03</t>
-  </si>
-  <si>
-    <t>Which traditional human-centred practices are described?</t>
-  </si>
-  <si>
-    <t>DS01Q04</t>
-  </si>
-  <si>
-    <t>Which technology‑enabled practices have been described?</t>
-  </si>
-  <si>
-    <t>DS01Q05</t>
-  </si>
-  <si>
-    <t>which emerging technologies have been described?</t>
-  </si>
-  <si>
-    <t>DS01Q06</t>
   </si>
   <si>
     <t>Which internal prerequisites are stated as necessary for technology-enable practices?</t>
@@ -1558,7 +1299,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF1F1F1F"/>
       <name val="Calibri"/>
@@ -1566,6 +1306,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF1F1F1F"/>
       <name val="Calibri"/>
@@ -2234,7 +1975,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2250,9 +1991,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2281,18 +2019,12 @@
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2300,6 +2032,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2826,150 +2561,68 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="3"/>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="3" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="7.6796875" style="21" customWidth="1"/>
-    <col min="2" max="2" width="25.125" customWidth="1"/>
-    <col min="3" max="3" width="32.546875" customWidth="1"/>
-    <col min="4" max="4" width="49.078125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="28.25" customWidth="1"/>
+    <col min="3" max="3" width="46.0859375" customWidth="1"/>
+    <col min="4" max="4" width="45.4375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:4">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="68" spans="1:4">
-      <c r="A2" s="13" t="s">
+    <row r="2" ht="168" spans="1:4">
+      <c r="A2" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="17" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" ht="51" spans="1:4">
-      <c r="A3" s="13" t="s">
+    <row r="3" ht="84" spans="1:4">
+      <c r="A3" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="17" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" ht="68" spans="1:4">
-      <c r="A4" s="13" t="s">
+    <row r="4" ht="168" spans="1:4">
+      <c r="A4" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="17" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="5" ht="68" spans="1:4">
-      <c r="A5" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" ht="68" spans="1:4">
-      <c r="A6" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" ht="51" spans="1:4">
-      <c r="A7" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" ht="51" spans="1:4">
-      <c r="A8" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" ht="68" spans="1:4">
-      <c r="A9" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" ht="34" spans="1:4">
-      <c r="A10" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -2981,122 +2634,153 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="30.59375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="62.7578125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="36.4453125" style="5" customWidth="1"/>
+    <col min="1" max="1" width="28.1171875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="27.078125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="41.53125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="36.4453125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.75" spans="1:3">
-      <c r="A1" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="B1" s="7" t="s">
+    <row r="1" ht="17.75" spans="1:4">
+      <c r="A1" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" ht="68.75" spans="1:4">
+      <c r="A2" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="3" ht="68.75" spans="1:4">
+      <c r="A3" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="4" ht="51.75" spans="1:4">
+      <c r="A4" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="5" ht="68.75" spans="1:4">
+      <c r="A5" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="6" ht="68.75" spans="1:4">
+      <c r="A6" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="7" ht="34.75" spans="1:4">
+      <c r="A7" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="D7" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" ht="51.75" spans="1:3">
-      <c r="A2" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="3" ht="68.75" spans="1:3">
-      <c r="A3" s="12" t="s">
-        <v>267</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="4" ht="51.75" spans="1:3">
-      <c r="A4" s="12" t="s">
-        <v>270</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>271</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="5" ht="68.75" spans="1:3">
-      <c r="A5" s="12" t="s">
-        <v>273</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="6" ht="51.75" spans="1:3">
-      <c r="A6" s="12" t="s">
-        <v>276</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>277</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="7" ht="17.75" spans="1:3">
-      <c r="A7" s="12" t="s">
-        <v>279</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>280</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="8" ht="51.75" spans="1:3">
-      <c r="A8" s="12" t="s">
-        <v>282</v>
+    </row>
+    <row r="8" ht="51.75" spans="1:4">
+      <c r="A8" s="11" t="s">
+        <v>250</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>283</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="9" ht="34.75" spans="1:3">
-      <c r="A9" s="12" t="s">
-        <v>285</v>
+        <v>250</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="9" ht="34.75" spans="1:4">
+      <c r="A9" s="11" t="s">
+        <v>253</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>286</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="10" ht="68.75" spans="1:3">
-      <c r="A10" s="12" t="s">
-        <v>288</v>
+        <v>253</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="10" ht="68.75" spans="1:4">
+      <c r="A10" s="11" t="s">
+        <v>256</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>289</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>290</v>
+        <v>256</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -3108,209 +2792,302 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="29.1640625" style="5" customWidth="1"/>
-    <col min="2" max="3" width="36.5859375" style="5" customWidth="1"/>
+    <col min="1" max="1" width="25.5234375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.7734375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="34.5" style="1" customWidth="1"/>
+    <col min="4" max="5" width="36.5859375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.75" spans="1:3">
-      <c r="A1" s="6" t="s">
+    <row r="1" ht="17.75" spans="1:5">
+      <c r="A1" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" ht="46.75" spans="1:5">
+      <c r="A2" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="3" ht="61.75" spans="1:5">
+      <c r="A3" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="4" ht="61.75" spans="1:5">
+      <c r="A4" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="5" ht="61.75" spans="1:5">
+      <c r="A5" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="6" ht="46.75" spans="1:5">
+      <c r="A6" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="7" ht="46.75" spans="1:5">
+      <c r="A7" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="8" ht="46.75" spans="1:5">
+      <c r="A8" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="9" ht="61.75" spans="1:5">
+      <c r="A9" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="10" ht="61.75" spans="1:5">
+      <c r="A10" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>291</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="E10" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" ht="46.75" spans="1:3">
-      <c r="A2" s="8" t="s">
+    </row>
+    <row r="11" ht="61.75" spans="1:5">
+      <c r="A11" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B11" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="D11" s="8" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="3" ht="46.75" spans="1:3">
-      <c r="A3" s="8" t="s">
+      <c r="E11" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="B3" s="9" t="s">
+    </row>
+    <row r="12" ht="46.75" spans="1:5">
+      <c r="A12" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="B12" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="D12" s="8" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="4" ht="61.75" spans="1:3">
-      <c r="A4" s="8" t="s">
+      <c r="E12" s="8" t="s">
         <v>299</v>
       </c>
-      <c r="B4" s="9" t="s">
+    </row>
+    <row r="13" ht="46.75" spans="1:5">
+      <c r="A13" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="B13" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="5" ht="61.75" spans="1:3">
-      <c r="A5" s="8" t="s">
+      <c r="E13" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="B5" s="9" t="s">
+    </row>
+    <row r="14" ht="46.75" spans="1:5">
+      <c r="A14" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="B14" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="D14" s="8" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="6" ht="61.75" spans="1:3">
-      <c r="A6" s="8" t="s">
+      <c r="E14" s="8" t="s">
         <v>305</v>
       </c>
-      <c r="B6" s="9" t="s">
+    </row>
+    <row r="15" ht="46.75" spans="1:5">
+      <c r="A15" s="7" t="s">
         <v>306</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="B15" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="D15" s="8" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="7" ht="46.75" spans="1:3">
-      <c r="A7" s="8" t="s">
+      <c r="E15" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="B7" s="9" t="s">
+    </row>
+    <row r="16" ht="46.75" spans="1:5">
+      <c r="A16" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="B16" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="D16" s="8" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="8" ht="46.75" spans="1:3">
-      <c r="A8" s="8" t="s">
+      <c r="E16" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="B8" s="9" t="s">
+    </row>
+    <row r="17" ht="61.75" spans="1:5">
+      <c r="A17" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="B17" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="D17" s="8" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="9" ht="46.75" spans="1:3">
-      <c r="A9" s="8" t="s">
+      <c r="E17" s="8" t="s">
         <v>314</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>315</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="10" ht="61.75" spans="1:3">
-      <c r="A10" s="8" t="s">
-        <v>317</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="11" ht="61.75" spans="1:3">
-      <c r="A11" s="8" t="s">
-        <v>320</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>321</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="12" ht="61.75" spans="1:3">
-      <c r="A12" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>324</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="13" ht="46.75" spans="1:3">
-      <c r="A13" s="8" t="s">
-        <v>326</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>327</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="14" ht="46.75" spans="1:3">
-      <c r="A14" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>330</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="15" ht="46.75" spans="1:3">
-      <c r="A15" s="8" t="s">
-        <v>332</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>333</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="16" ht="46.75" spans="1:3">
-      <c r="A16" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>336</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="17" ht="46.75" spans="1:3">
-      <c r="A17" s="8" t="s">
-        <v>338</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>339</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="18" ht="61.75" spans="1:3">
-      <c r="A18" s="8" t="s">
-        <v>341</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>342</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>343</v>
       </c>
     </row>
   </sheetData>
@@ -3337,351 +3114,351 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>344</v>
+        <v>315</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>345</v>
+        <v>316</v>
       </c>
     </row>
     <row r="2" s="2" customFormat="1" ht="17" spans="1:3">
       <c r="A2" s="4" t="s">
-        <v>346</v>
+        <v>317</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>267</v>
+        <v>318</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>347</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" s="2" customFormat="1" ht="17" spans="1:3">
       <c r="A3" s="4" t="s">
-        <v>348</v>
+        <v>320</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>270</v>
+        <v>238</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>349</v>
+        <v>321</v>
       </c>
     </row>
     <row r="4" s="2" customFormat="1" ht="34" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>350</v>
+        <v>322</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>273</v>
+        <v>323</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>351</v>
+        <v>324</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1" ht="34" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>352</v>
+        <v>325</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>276</v>
+        <v>326</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1" ht="34" spans="1:3">
       <c r="A6" s="4" t="s">
-        <v>354</v>
+        <v>328</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>279</v>
+        <v>247</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>355</v>
+        <v>329</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" ht="34" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>356</v>
+        <v>330</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>282</v>
+        <v>331</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>357</v>
+        <v>332</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" ht="51" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>358</v>
+        <v>333</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>285</v>
+        <v>253</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>359</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" ht="17" spans="1:3">
       <c r="A9" s="4" t="s">
-        <v>360</v>
+        <v>335</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>288</v>
+        <v>256</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>361</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" ht="34" spans="1:3">
       <c r="A10" s="4" t="s">
-        <v>362</v>
+        <v>337</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>302</v>
+        <v>268</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>363</v>
+        <v>338</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" ht="34" spans="1:3">
       <c r="A11" s="4" t="s">
-        <v>364</v>
+        <v>339</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>305</v>
+        <v>272</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>365</v>
+        <v>340</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" ht="34" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>366</v>
+        <v>341</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>308</v>
+        <v>275</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>367</v>
+        <v>342</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" ht="51" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>368</v>
+        <v>343</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>311</v>
+        <v>278</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>369</v>
+        <v>344</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" ht="34" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>370</v>
+        <v>345</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>314</v>
+        <v>282</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>371</v>
+        <v>346</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" ht="34" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>372</v>
+        <v>347</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>317</v>
+        <v>285</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>373</v>
+        <v>348</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" ht="34" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>374</v>
+        <v>349</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>320</v>
+        <v>289</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>375</v>
+        <v>350</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" ht="34" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>376</v>
+        <v>351</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>323</v>
+        <v>293</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>377</v>
+        <v>352</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" ht="34" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>378</v>
+        <v>353</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>326</v>
+        <v>297</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>379</v>
+        <v>354</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" ht="51" spans="1:3">
       <c r="A19" s="4" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>329</v>
+        <v>300</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>381</v>
+        <v>356</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" ht="34" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>382</v>
+        <v>357</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>332</v>
+        <v>303</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>383</v>
+        <v>358</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" ht="34" spans="1:3">
       <c r="A21" s="4" t="s">
-        <v>384</v>
+        <v>359</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>335</v>
+        <v>306</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>385</v>
+        <v>360</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" ht="51" spans="1:3">
       <c r="A22" s="4" t="s">
-        <v>386</v>
+        <v>361</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>338</v>
+        <v>309</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>387</v>
+        <v>362</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" ht="34" spans="1:3">
       <c r="A23" s="4" t="s">
-        <v>388</v>
+        <v>363</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>341</v>
+        <v>312</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>389</v>
+        <v>364</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" ht="101" spans="1:3">
       <c r="A24" s="4" t="s">
-        <v>390</v>
+        <v>365</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>391</v>
+        <v>366</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>392</v>
+        <v>367</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" ht="101" spans="1:3">
       <c r="A25" s="4" t="s">
-        <v>393</v>
+        <v>368</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>391</v>
+        <v>366</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>394</v>
+        <v>369</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" ht="68" spans="1:3">
       <c r="A26" s="4" t="s">
-        <v>395</v>
+        <v>370</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>396</v>
+        <v>371</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>397</v>
+        <v>372</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" ht="68" spans="1:3">
       <c r="A27" s="4" t="s">
-        <v>398</v>
+        <v>373</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>396</v>
+        <v>371</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>399</v>
+        <v>374</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" ht="68" spans="1:3">
       <c r="A28" s="4" t="s">
-        <v>400</v>
+        <v>375</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>401</v>
+        <v>376</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>402</v>
+        <v>377</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1" ht="68" spans="1:3">
       <c r="A29" s="4" t="s">
-        <v>403</v>
+        <v>378</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>401</v>
+        <v>376</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>404</v>
+        <v>379</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" ht="51" spans="1:3">
       <c r="A30" s="4" t="s">
-        <v>405</v>
+        <v>380</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>406</v>
+        <v>381</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>407</v>
+        <v>382</v>
       </c>
     </row>
     <row r="31" s="2" customFormat="1" ht="51" spans="1:3">
       <c r="A31" s="4" t="s">
-        <v>408</v>
+        <v>383</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>406</v>
+        <v>381</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>409</v>
+        <v>384</v>
       </c>
     </row>
     <row r="32" s="2" customFormat="1" ht="68" spans="1:3">
       <c r="A32" s="4" t="s">
-        <v>410</v>
+        <v>385</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>406</v>
+        <v>381</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>411</v>
+        <v>386</v>
       </c>
     </row>
   </sheetData>
@@ -3702,46 +3479,46 @@
   <sheetData>
     <row r="1" ht="17" spans="1:3">
       <c r="A1" t="s">
-        <v>412</v>
+        <v>387</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>413</v>
+        <v>388</v>
       </c>
       <c r="C1" t="s">
-        <v>414</v>
+        <v>389</v>
       </c>
     </row>
     <row r="2" ht="168" spans="1:3">
       <c r="A2" t="s">
-        <v>415</v>
+        <v>390</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>416</v>
+        <v>391</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>417</v>
+        <v>392</v>
       </c>
     </row>
     <row r="3" ht="202" spans="1:3">
       <c r="A3" t="s">
-        <v>418</v>
+        <v>393</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>419</v>
+        <v>394</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>420</v>
+        <v>395</v>
       </c>
     </row>
     <row r="4" ht="152" spans="1:3">
       <c r="A4" t="s">
-        <v>421</v>
+        <v>396</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>422</v>
+        <v>397</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>423</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>
@@ -3753,189 +3530,152 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="3"/>
   <cols>
-    <col min="2" max="2" width="31.109375" customWidth="1"/>
-    <col min="3" max="3" width="36.8515625" customWidth="1"/>
-    <col min="4" max="4" width="49.21875" customWidth="1"/>
+    <col min="1" max="1" width="7.6796875" style="18" customWidth="1"/>
+    <col min="2" max="2" width="25.125" customWidth="1"/>
+    <col min="3" max="3" width="32.546875" customWidth="1"/>
+    <col min="4" max="4" width="49.078125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:4">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="34" spans="1:4">
-      <c r="A2" s="20" t="s">
+    <row r="2" ht="68" spans="1:4">
+      <c r="A2" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" ht="51" spans="1:4">
+      <c r="A3" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" ht="68" spans="1:4">
+      <c r="A4" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" ht="68" spans="1:4">
+      <c r="A5" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" ht="68" spans="1:4">
+      <c r="A6" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" ht="51" spans="1:4">
+      <c r="A7" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="14" t="s">
+    </row>
+    <row r="8" ht="51" spans="1:4">
+      <c r="A8" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="B8" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="C8" s="13" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="3" ht="34" spans="1:4">
-      <c r="A3" s="20" t="s">
+      <c r="D8" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="14" t="s">
+    </row>
+    <row r="9" ht="68" spans="1:4">
+      <c r="A9" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="B9" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C9" s="13" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="4" ht="34" spans="1:4">
-      <c r="A4" s="20" t="s">
+      <c r="D9" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="14" t="s">
+    </row>
+    <row r="10" ht="34" spans="1:4">
+      <c r="A10" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="B10" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="C10" s="13" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="5" ht="34" spans="1:4">
-      <c r="A5" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" ht="34" spans="1:4">
-      <c r="A6" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" s="20"/>
-    </row>
-    <row r="7" ht="17" spans="1:4">
-      <c r="A7" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" ht="34" spans="1:4">
-      <c r="A8" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" ht="34" spans="1:4">
-      <c r="A9" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="10" customFormat="1" ht="34" spans="1:4">
-      <c r="A10" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="11" customFormat="1" ht="34" spans="1:4">
-      <c r="A11" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="D11" s="20"/>
-    </row>
-    <row r="12" ht="34" spans="1:4">
-      <c r="A12" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="13" ht="34" spans="1:4">
-      <c r="A13" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="D13" s="20"/>
+      <c r="D10" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3951,162 +3691,162 @@
   <cols>
     <col min="1" max="1" width="9.8984375" customWidth="1"/>
     <col min="2" max="2" width="14.84375" customWidth="1"/>
-    <col min="3" max="3" width="62.6328125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="32.5546875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="62.6328125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.5546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="17" spans="1:4">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" ht="68" spans="1:4">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" ht="68" spans="1:4">
+      <c r="A3" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" ht="68" spans="1:4">
+      <c r="A4" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" ht="68" spans="1:4">
+      <c r="A5" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" ht="68" spans="1:4">
+      <c r="A6" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" ht="68" spans="1:4">
+      <c r="A7" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" ht="68" spans="1:4">
+      <c r="A8" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" ht="68" spans="1:4">
+      <c r="A9" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" ht="68" spans="1:4">
+      <c r="A10" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="C10" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="D10" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="D2" s="20" t="s">
+    </row>
+    <row r="11" ht="68" spans="1:4">
+      <c r="A11" s="16" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="3" ht="68" spans="1:4">
-      <c r="A3" s="18" t="s">
+      <c r="B11" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="C11" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="D11" s="17" t="s">
         <v>90</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="4" ht="68" spans="1:4">
-      <c r="A4" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="5" ht="68" spans="1:4">
-      <c r="A5" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" ht="68" spans="1:4">
-      <c r="A6" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="7" ht="68" spans="1:4">
-      <c r="A7" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="8" ht="68" spans="1:4">
-      <c r="A8" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="9" ht="68" spans="1:4">
-      <c r="A9" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="C9" s="20" t="s">
-        <v>114</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="10" ht="68" spans="1:4">
-      <c r="A10" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>117</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="11" ht="68" spans="1:4">
-      <c r="A11" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>121</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -4127,82 +3867,82 @@
   </cols>
   <sheetData>
     <row r="1" ht="17" spans="1:4">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" ht="68" spans="1:4">
-      <c r="A2" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="B2" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>127</v>
+      <c r="A2" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="3" ht="68" spans="1:4">
-      <c r="A3" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>131</v>
+      <c r="A3" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="4" ht="68" spans="1:4">
-      <c r="A4" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="D4" s="20"/>
+      <c r="A4" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="D4" s="17"/>
     </row>
     <row r="5" ht="101" spans="1:4">
-      <c r="A5" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>137</v>
-      </c>
-      <c r="D5" s="20"/>
-    </row>
-    <row r="6" ht="101" spans="1:4">
-      <c r="A6" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="D6" s="20"/>
+      <c r="A5" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="D5" s="17"/>
+    </row>
+    <row r="6" ht="34" spans="1:4">
+      <c r="A6" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="D6" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4222,112 +3962,112 @@
   </cols>
   <sheetData>
     <row r="1" ht="17" spans="1:4">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="D2" s="18"/>
+      <c r="A2" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="D2" s="16"/>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="D3" s="18"/>
+      <c r="A3" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="D3" s="16"/>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="D4" s="18"/>
+      <c r="A4" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="D4" s="16"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="D5" s="18"/>
+      <c r="A5" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="D5" s="16"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="D6" s="18"/>
+      <c r="A6" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="D6" s="16"/>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>156</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="D7" s="18"/>
+      <c r="A7" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="D7" s="16"/>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="D8" s="18"/>
+      <c r="A8" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="D8" s="16"/>
     </row>
     <row r="9" customFormat="1" ht="17" spans="1:4">
-      <c r="A9" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>162</v>
+      <c r="A9" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -4348,172 +4088,172 @@
   </cols>
   <sheetData>
     <row r="1" ht="17" spans="1:4">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="D2" s="15"/>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="D3" s="15"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="D4" s="15"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="D5" s="15"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="D6" s="15"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D7" s="15"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="D8" s="15"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="D9" s="15"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="D10" s="15"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="D11" s="15"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="D12" s="15"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B13" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C13" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="D2" s="19"/>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="19" t="s">
+      <c r="D13" s="15"/>
+    </row>
+    <row r="14" ht="17" spans="1:4">
+      <c r="A14" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B14" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="13" t="s">
         <v>167</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="D3" s="19"/>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="D4" s="19"/>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>173</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="D5" s="19"/>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="19" t="s">
-        <v>175</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="D6" s="19"/>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>180</v>
-      </c>
-      <c r="D7" s="19"/>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="D8" s="19"/>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="19" t="s">
-        <v>184</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>185</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>186</v>
-      </c>
-      <c r="D9" s="19"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>188</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="D10" s="19"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="19" t="s">
-        <v>190</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>192</v>
-      </c>
-      <c r="D11" s="19"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>194</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>195</v>
-      </c>
-      <c r="D12" s="19"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>197</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>198</v>
-      </c>
-      <c r="D13" s="19"/>
-    </row>
-    <row r="14" ht="17" spans="1:4">
-      <c r="A14" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -4534,48 +4274,48 @@
   </cols>
   <sheetData>
     <row r="1" ht="17" spans="1:4">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
+      <c r="A2" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="17" t="s">
-        <v>203</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>204</v>
-      </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
+      <c r="A3" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="17" t="s">
-        <v>205</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>206</v>
-      </c>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
+      <c r="A4" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4596,218 +4336,218 @@
   </cols>
   <sheetData>
     <row r="1" ht="17" spans="1:5">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="2" ht="68" spans="1:5">
+      <c r="A2" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="3" ht="68" spans="1:5">
+      <c r="A3" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4" ht="68" spans="1:5">
+      <c r="A4" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="5" ht="68" spans="1:5">
+      <c r="A5" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="6" ht="84" spans="1:5">
+      <c r="A6" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="7" ht="68" spans="1:5">
+      <c r="A7" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="8" ht="68" spans="1:5">
+      <c r="A8" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="9" ht="68" spans="1:5">
+      <c r="A9" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="10" ht="68" spans="1:5">
+      <c r="A10" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="11" ht="68" spans="1:5">
+      <c r="A11" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="12" ht="51" spans="1:5">
+      <c r="A12" s="4" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="2" ht="68" spans="1:5">
-      <c r="A2" s="16" t="s">
+      <c r="B12" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="C12" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="D12" s="4"/>
+      <c r="E12" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="13" ht="68" spans="1:5">
+      <c r="A13" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16" t="s">
+      <c r="B13" s="4" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="3" ht="68" spans="1:5">
-      <c r="A3" s="16" t="s">
+      <c r="C13" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="D13" s="4"/>
+      <c r="E13" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="14" ht="17" spans="1:5">
+      <c r="A14" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="B14" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="4" ht="68" spans="1:5">
-      <c r="A4" s="16" t="s">
-        <v>215</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>216</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>217</v>
-      </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="5" ht="68" spans="1:5">
-      <c r="A5" s="16" t="s">
-        <v>218</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>219</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="6" ht="84" spans="1:5">
-      <c r="A6" s="16" t="s">
-        <v>222</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>223</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>224</v>
-      </c>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="7" ht="68" spans="1:5">
-      <c r="A7" s="16" t="s">
-        <v>225</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>226</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>227</v>
-      </c>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="8" ht="68" spans="1:5">
-      <c r="A8" s="16" t="s">
-        <v>228</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>229</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="9" ht="68" spans="1:5">
-      <c r="A9" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>232</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>233</v>
-      </c>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="10" ht="68" spans="1:5">
-      <c r="A10" s="16" t="s">
-        <v>234</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>235</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>236</v>
-      </c>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="11" ht="68" spans="1:5">
-      <c r="A11" s="16" t="s">
-        <v>237</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>238</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>239</v>
-      </c>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="12" ht="51" spans="1:5">
-      <c r="A12" s="16" t="s">
-        <v>240</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>241</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>242</v>
-      </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="13" ht="68" spans="1:5">
-      <c r="A13" s="16" t="s">
-        <v>243</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>244</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>245</v>
-      </c>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="14" ht="68" spans="1:5">
-      <c r="A14" s="16" t="s">
-        <v>246</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>247</v>
-      </c>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E13" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A2:E13">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E14" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A1:E14">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>
@@ -4823,64 +4563,64 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="4" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="17.4453125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="32.8125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="40.8828125" style="5" customWidth="1"/>
+    <col min="1" max="1" width="17.4453125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.8125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="40.8828125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="17" spans="1:3">
-      <c r="A1" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>249</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>250</v>
+      <c r="A1" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="2" ht="51" spans="1:3">
-      <c r="A2" s="14" t="s">
-        <v>251</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>252</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>253</v>
+      <c r="A2" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="3" ht="68" spans="1:3">
-      <c r="A3" s="14" t="s">
-        <v>254</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>255</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>256</v>
+      <c r="A3" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="4" ht="68" spans="1:3">
-      <c r="A4" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>258</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>259</v>
+      <c r="A4" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="5" ht="68" spans="1:3">
-      <c r="A5" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>261</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>262</v>
+      <c r="A5" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>229</v>
       </c>
     </row>
   </sheetData>

--- a/src/conf/coding_schema/coding_schema.xlsx
+++ b/src/conf/coding_schema/coding_schema.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11040"/>
+    <workbookView windowWidth="28800" windowHeight="11060"/>
   </bookViews>
   <sheets>
     <sheet name="Tacit Knowledge" sheetId="13" r:id="rId1"/>
@@ -105,7 +105,7 @@
     <t>TE01</t>
   </si>
   <si>
-    <t>Artificial Intelligence and Computational Intelligence</t>
+    <t>Artificial Intelligence and Intelligent Computation</t>
   </si>
   <si>
     <t>Foundational core models, connectionist AI, natural language processing architectures, and generative systems.</t>
@@ -141,7 +141,7 @@
     <t>TE04</t>
   </si>
   <si>
-    <t>Information Systems and Data Management</t>
+    <t>Data, Information, and Knowledge Systems</t>
   </si>
   <si>
     <t>The structural storage, architecture, indexing, retrieval, and semantic mapping of data and structural knowledge.</t>
@@ -153,7 +153,7 @@
     <t>TE05</t>
   </si>
   <si>
-    <t>Computer Vision, Sensing, and Perception</t>
+    <t>Imaging, Sensing, and Perception Technologies</t>
   </si>
   <si>
     <t>The hardware, telemetry, and signal/image processing algorithms required to capture and perceive environmental inputs.</t>
